--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/mlf/banco-30j-4m-5_60tr-constantd-50c_mlf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/mlf/banco-30j-4m-5_60tr-constantd-50c_mlf.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pago JE-980</t>
+          <t>Cambio de divisa QQ-997</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -479,12 +479,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consulta JE-629</t>
+          <t>Consulta EQ-485</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -500,12 +500,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cancelación QP-366</t>
+          <t>Reclamo QE-860</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -521,12 +521,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Consulta QP-318</t>
+          <t>Cambio de divisa PE-296</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -542,12 +542,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pago EP-018</t>
+          <t>Consulta PP-156</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -563,12 +563,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consulta PJ-398</t>
+          <t>Pago JE-303</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -584,12 +584,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pago PJ-433</t>
+          <t>Cancelación QJ-473</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -605,12 +605,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solicitud QQ-398</t>
+          <t>Pago EP-722</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -626,12 +626,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Retiro JJ-758</t>
+          <t>Retiro PJ-017</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -647,12 +647,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solicitud QP-497</t>
+          <t>Solicitud EP-995</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Danna Viviana</t>
+          <t>Saúl Vargas</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -668,12 +668,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cambio de divisa PQ-401</t>
+          <t>Cambio de divisa PJ-850</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -689,12 +689,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cancelación EP-605</t>
+          <t>Consulta PP-142</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -710,12 +710,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Retiro EP-850</t>
+          <t>Pago JP-602</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -731,12 +731,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Reclamo PJ-567</t>
+          <t>Reclamo EE-453</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -752,12 +752,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Reclamo PJ-698</t>
+          <t>Solicitud PQ-841</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -773,12 +773,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solicitud PP-459</t>
+          <t>Solicitud JP-055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -794,12 +794,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reclamo QP-496</t>
+          <t>Pago QE-560</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -815,12 +815,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cancelación QP-417</t>
+          <t>Consulta JJ-594</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -836,12 +836,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cancelación QP-155</t>
+          <t>Pago PQ-175</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -857,12 +857,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pago QP-426</t>
+          <t>Solicitud EP-628</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cristina Páez</t>
+          <t>Marcela Oliva</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -878,12 +878,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cambio de divisa JQ-930</t>
+          <t>Solicitud JJ-236</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -899,12 +899,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Reclamo JQ-620</t>
+          <t>Retiro PJ-015</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -920,12 +920,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cambio de divisa EP-070</t>
+          <t>Solicitud JQ-274</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -941,12 +941,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solicitud QE-991</t>
+          <t>Consulta QE-654</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -962,12 +962,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pago PE-286</t>
+          <t>Pago JQ-719</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -983,12 +983,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solicitud PQ-660</t>
+          <t>Cambio de divisa JQ-829</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1004,12 +1004,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solicitud QE-611</t>
+          <t>Consulta QJ-218</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1025,12 +1025,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solicitud QJ-833</t>
+          <t>Pago EQ-459</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1046,12 +1046,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Reclamo PP-250</t>
+          <t>Reclamo EE-457</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1067,12 +1067,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Retiro JP-049</t>
+          <t>Cambio de divisa JE-434</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C31" t="n">
